--- a/CapEx_2026.xlsx
+++ b/CapEx_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\jeeratheepk\Documents\ฝึกสร้างเว็บ\CapEx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\jeeratheepk\Desktop\ฝึกสร้างเว็บ\CapEx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="108">
   <si>
     <t>โรงงาน</t>
   </si>
@@ -272,13 +272,105 @@
   </si>
   <si>
     <t>%ความคืบหน้า</t>
+  </si>
+  <si>
+    <t>IO</t>
+  </si>
+  <si>
+    <t>งานสร้างอาคารพยาบาล SHE และสรรพสามิต</t>
+  </si>
+  <si>
+    <t>งานระบบท่อดับเพลิง Auto Sprinkler ถังจัดเก็บเอทานอลเพิ่มเติม</t>
+  </si>
+  <si>
+    <t>ต่อเติมอาคารโรงคัดแยกขยะสำหรับจัดเก็บถังน้ำมัน</t>
+  </si>
+  <si>
+    <t>ถังบรรจุโฟมดับเพลิงพร้อม Bund Wall และอุปกรณ์ดับเพลิง</t>
+  </si>
+  <si>
+    <t>ปรับรอบหม้อกรองอัตโนมัติตามระดับโคลน(AI)</t>
+  </si>
+  <si>
+    <t>Breather Valve (PSV411 &amp; PSV412)</t>
+  </si>
+  <si>
+    <t>Multifunction Calibrator</t>
+  </si>
+  <si>
+    <t>เครื่อง pH Meter &amp; Electrode for Ethanol samples</t>
+  </si>
+  <si>
+    <t>ติดตั้ง Inverter Boiler Feed Pump (BFP) 300 kW</t>
+  </si>
+  <si>
+    <t>รถแทรกเตอร์พร้อมอุปกรณ์ต่อพ่วงสำหรับตัดหญ้า</t>
+  </si>
+  <si>
+    <t>ปรับปรุงห้องทำงานอาคารศูนย์วิศวกรรมชั้น 2</t>
+  </si>
+  <si>
+    <t>ปรับปรุงห้องทำงานสำนักงานชั้น 2 (กั้นห้องHR)</t>
+  </si>
+  <si>
+    <t>MCE</t>
+  </si>
+  <si>
+    <t>251020000376
+251020000419</t>
+  </si>
+  <si>
+    <t>250010001148</t>
+  </si>
+  <si>
+    <t>250020000853</t>
+  </si>
+  <si>
+    <t>250020000854</t>
+  </si>
+  <si>
+    <t>250020000855</t>
+  </si>
+  <si>
+    <t>250020000856</t>
+  </si>
+  <si>
+    <t>พัดลมระบายอากาศห้องผสมสารเคมีและห้องแลป</t>
+  </si>
+  <si>
+    <t>250020000790</t>
+  </si>
+  <si>
+    <t>250010001146</t>
+  </si>
+  <si>
+    <t>250010001149</t>
+  </si>
+  <si>
+    <t>250010001147</t>
+  </si>
+  <si>
+    <t>250020000864</t>
+  </si>
+  <si>
+    <t>250020000863</t>
+  </si>
+  <si>
+    <t>253020000063</t>
+  </si>
+  <si>
+    <t>253020000064</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,19 +386,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -318,35 +426,311 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma 2" xfId="1"/>
+    <cellStyle name="Comma 3" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -357,6 +741,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I39" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:I39"/>
+  <sortState ref="A2:H26">
+    <sortCondition ref="C1:C26"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" name="ประเภท" dataDxfId="10"/>
+    <tableColumn id="2" name="โครงการ" dataDxfId="9"/>
+    <tableColumn id="3" name="โรงงาน" dataDxfId="8"/>
+    <tableColumn id="4" name="งบประมาณ" dataDxfId="7"/>
+    <tableColumn id="5" name="วัตถุประสงค์" dataDxfId="6"/>
+    <tableColumn id="6" name="ประโยชน์ที่ได้รับ" dataDxfId="5"/>
+    <tableColumn id="7" name="%IRR/NPV/PB" dataDxfId="4"/>
+    <tableColumn id="8" name="%ความคืบหน้า" dataDxfId="3"/>
+    <tableColumn id="10" name="IO" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -622,661 +1027,942 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="38.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="70.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="104.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="148.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="104.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="148.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="29">
+      <c r="I1" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="29">
       <c r="A2" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2">
-        <v>100000</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>65</v>
+        <v>350000</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="29">
+        <v>72</v>
+      </c>
+      <c r="H2" s="8">
+        <v>5</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="29">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2">
-        <v>370000</v>
+        <v>460000</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
+        <v>20</v>
+      </c>
+      <c r="H3" s="8">
+        <v>20</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2">
-        <v>350000</v>
+        <v>130000</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="8">
+        <v>35</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1">
+      <c r="A5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2">
+        <v>300000</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1">
+      <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="8">
+        <v>100</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="29">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2255000</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="29">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2">
-        <v>110000</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="29">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2">
-        <v>1200000</v>
+        <v>160000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="29">
+        <v>52</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="29">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="2">
-        <v>460000</v>
+        <v>1490000</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8">
+        <v>61</v>
+      </c>
+      <c r="H8" s="8">
+        <v>5</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1">
+      <c r="A9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2">
+        <v>400000</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="8">
+        <v>10</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1">
+      <c r="B10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2">
+        <v>250000</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="8">
+        <v>15</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1430000</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="1" customFormat="1">
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <v>450000</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="2">
+        <v>920000</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="1" customFormat="1">
+      <c r="A15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="2">
+        <v>945000</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2">
+        <v>100000</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="8">
+        <v>5</v>
+      </c>
+      <c r="I16" s="10">
+        <v>250010001150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2">
+        <v>370000</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="8">
+        <v>10</v>
+      </c>
+      <c r="I17" s="10">
+        <v>250020000857</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2255000</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="8">
+        <v>5</v>
+      </c>
+      <c r="I18" s="10">
+        <v>250020000858</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2">
+        <v>110000</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="8">
+        <v>5</v>
+      </c>
+      <c r="I19" s="10">
+        <v>250020000859</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="1" customFormat="1">
+      <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="8">
+        <v>5</v>
+      </c>
+      <c r="I20" s="10">
+        <v>250020000860</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="2">
+        <v>28000</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="8">
+        <v>15</v>
+      </c>
+      <c r="I21" s="10">
+        <v>250010001151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="1" customFormat="1">
+      <c r="A22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="2">
+        <v>140000</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="8">
+        <v>50</v>
+      </c>
+      <c r="I22" s="10">
+        <v>250010001152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="1" customFormat="1">
+      <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="8">
+        <v>100</v>
+      </c>
+      <c r="I23" s="10">
+        <v>250010001153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="A24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2">
+        <v>80000</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="8">
+        <v>50</v>
+      </c>
+      <c r="I24" s="10">
+        <v>250010001154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="1" customFormat="1">
+      <c r="A25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="29">
-      <c r="A10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2">
-        <v>28000</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2">
-        <v>140000</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2">
-        <v>20000</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="29">
-      <c r="A13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="2">
-        <v>80000</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="2">
-        <v>20000</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2">
-        <v>130000</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2">
-        <v>300000</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2">
-        <v>20000</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="29">
-      <c r="A18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2">
-        <v>160000</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="29">
-      <c r="A19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="2">
-        <v>982000</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="29">
-      <c r="A20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="2">
-        <v>920000</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="29">
-      <c r="A21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1430000</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="H21">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="29">
-      <c r="A22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1490000</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="2">
-        <v>370000</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="H23">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="2">
-        <v>945000</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24" s="1"/>
-      <c r="H24">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2">
-        <v>450000</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="H25" s="8">
+        <v>5</v>
+      </c>
+      <c r="I25" s="10">
+        <v>250010001155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="29">
       <c r="A26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="2">
+        <v>982000</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="8">
+        <v>5</v>
+      </c>
+      <c r="I26" s="10">
+        <v>250020000861</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="1" customFormat="1">
+      <c r="A27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="2">
-        <v>400000</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="2">
+        <v>370000</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="D27" s="6"/>
+      <c r="H27" s="8">
+        <v>5</v>
+      </c>
+      <c r="I27" s="10">
+        <v>250020000862</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="29">
+      <c r="B28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2855104.32</v>
+      </c>
+      <c r="H28" s="8">
+        <v>97</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="1" customFormat="1">
+      <c r="B29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2610000</v>
+      </c>
+      <c r="H29" s="8">
+        <v>87</v>
+      </c>
+      <c r="I29" s="7">
+        <v>251020000329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="1" customFormat="1">
+      <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3496000</v>
+      </c>
+      <c r="H30" s="8">
+        <v>25</v>
+      </c>
+      <c r="I30" s="7">
+        <v>251020000406</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="1" customFormat="1">
+      <c r="B31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="2">
+        <v>600000</v>
+      </c>
+      <c r="H31" s="8">
+        <v>100</v>
+      </c>
+      <c r="I31" s="7">
+        <v>251020000407</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="1" customFormat="1">
+      <c r="B32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="2">
+        <v>640000</v>
+      </c>
+      <c r="H32" s="8">
+        <v>91</v>
+      </c>
+      <c r="I32" s="7">
+        <v>251020000420</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="1" customFormat="1">
+      <c r="B33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="2">
+        <v>650000</v>
+      </c>
+      <c r="H33" s="8">
+        <v>5</v>
+      </c>
+      <c r="I33" s="7">
+        <v>251020000461</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" s="1" customFormat="1">
+      <c r="B34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="2">
+        <v>120000</v>
+      </c>
+      <c r="H34" s="8">
+        <v>100</v>
+      </c>
+      <c r="I34" s="7">
+        <v>251010000713</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" s="1" customFormat="1">
+      <c r="B35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="2">
+        <v>222200</v>
+      </c>
+      <c r="H35" s="8">
+        <v>5</v>
+      </c>
+      <c r="I35" s="7">
+        <v>251010000714</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" s="1" customFormat="1">
+      <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="2">
+        <v>900000</v>
+      </c>
+      <c r="H36" s="8">
+        <v>5</v>
+      </c>
+      <c r="I36" s="7">
+        <v>251020000462</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" s="1" customFormat="1">
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="2">
+        <v>278500</v>
+      </c>
+      <c r="H37" s="8">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7">
+        <v>251010000715</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="1" customFormat="1">
+      <c r="B38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="2">
+        <v>225000</v>
+      </c>
+      <c r="H38" s="8">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7">
+        <v>251020000463</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="1" customFormat="1">
+      <c r="B39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="2">
+        <v>85000</v>
+      </c>
+      <c r="H39" s="8">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>251020000464</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>